--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_display_v8【迷宫-技能-效果展示信息】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_display_v8【迷宫-技能-效果展示信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E706EE32-2EFB-4F61-BA62-1041048EDAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74057853-5081-4AEC-96F2-52AB6B572AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_effect_display_v8" sheetId="1" r:id="rId1"/>
@@ -207,11 +207,11 @@
     <t>fang_bao</t>
   </si>
   <si>
-    <t>回复生命</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>bu_mian</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复生命</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -790,16 +790,16 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
